--- a/Red5-DHCP_BMS_IO_List.xlsx
+++ b/Red5-DHCP_BMS_IO_List.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -621,42 +621,54 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>BMS platform</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Azbil savic-netFX2 (savic-net FX2), S/W 機能仕様 dated 2015/04/09 — confirmed from the 144-page Azbil 納入仕様書 (software function spec, not an equipment list)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Sheets</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Panels · Controllers · IO_List · IO_Summary · Legend</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Sheets</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>As-built M-01 equipment schedule, 共-01 ESCO spec, 空調機スケジュール_20251127.xlsx</t>
+          <t>Panels · Controllers · IO_List · IO_Summary · Legend</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>As-built M-01 equipment schedule, 共-01 ESCO spec, 空調機スケジュール_20251127.xlsx, Azbil savic-netFX2 S/W 納入仕様書 (platform + supervisory functions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Items marked 'INFERRED' (secondary/HW pumps, FCU quantity) must be confirmed against as-builts / Azbil 納入仕様書.</t>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Items marked 'INFERRED' (secondary/HW pumps, FCU quantity) must be confirmed against the M-01 mechanical equipment schedule in the as-built set — they are NOT in the Azbil 納入仕様書 (that is the savic-netFX2 software function spec).</t>
         </is>
       </c>
     </row>
@@ -722,7 +734,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Central monitoring server (中央監視)</t>
+          <t>Azbil savic-netFX2 central monitoring (中央監視)</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -732,7 +744,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Whole-building supervisory, alarms, trends, schedules, energy</t>
+          <t>Whole-building supervisory on savic-netFX2 (S/W spec 2015/04/09): point mgmt, start-stop/setpoint operation, status &amp; alarm/event processing, time-program + calendar + event-program control, seasonal changeover (batch), remote-setpoint schedules, runtime/start-count &amp; deviation/hi-lo limit monitoring, trend + periodic data collection, daily/monthly reports, energy CSV export, numeric/logic operations, power-failure/restoration handling, user/access mgmt, maintenance &amp; spare-parts mgmt</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">

--- a/Red5-DHCP_BMS_IO_List.xlsx
+++ b/Red5-DHCP_BMS_IO_List.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>R-1 single water-cooled chiller (Ebara ~370 kW, COP 4.51) in changeover with DHC via HEX-1 + CP-8; CDP-3 + CT-3 condenser; CP-7 CHW; HP-4 + EX4 + EXT-3 secondary; 2 source-changeover valves</t>
+          <t>R-1 single water-cooled SCREW chiller (Ebara RHS DW202M2, 370 kW / 82.2 kW in / COP 4.5, twin 45 kW screw comp, R-407C) in changeover with DHC via HEX-1 + CP-8; CDP-3 + CT-3 condenser; CP-7 CHW; HP-4 + EX4 + EXT-3 secondary; 2 source-changeover valves</t>
         </is>
       </c>
     </row>
@@ -21751,7 +21751,7 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
@@ -21816,7 +21816,7 @@
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E284" s="8" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E286" s="8" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
@@ -22080,7 +22080,7 @@
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E288" s="8" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
@@ -22222,7 +22222,7 @@
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E290" s="8" t="inlineStr">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="O291" s="8" t="inlineStr">
         <is>
-          <t>For COP; nameplate 370 kW / COP 4.51</t>
+          <t>Ebara screw RHS DW202M2: 370 kW cool / 82.2 kW in (COP 4.5); 2×45 kW screw comp, R-407C</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Water-cooled chiller (local backup)</t>
+          <t>Water-cooled screw chiller (local backup)</t>
         </is>
       </c>
       <c r="E292" s="8" t="inlineStr">
@@ -80985,7 +80985,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Local 36/37F water-cooled chiller (Ebara ~370 kW, COP 4.51), DHC-backup</t>
+          <t>Local 36/37F water-cooled SCREW chiller — Ebara RHS DW202M2 (370 kW, COP 4.5, twin screw, R-407C), DHC-backup</t>
         </is>
       </c>
     </row>
